--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_45912D5ECFA25FB81907AB4E1431840BEC67E453" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC2628B5-727D-4318-8F35-93A63AB42CDF}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_45912D5ECFA25FB81907AB4E1431840BEC67E453" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FFAC53-C71D-492B-A69E-97EB0036F9D6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -655,9 +655,6 @@
     <t>COMPRA      PATAGONIA</t>
   </si>
   <si>
-    <t>CEN</t>
-  </si>
-  <si>
     <t>REDIVA 19210ANCAP AROCEN</t>
   </si>
   <si>
@@ -2477,6 +2474,9 @@
   </si>
   <si>
     <t>Nafta · Peaje · Otro</t>
+  </si>
+  <si>
+    <t>ANCAP</t>
   </si>
 </sst>
 </file>
@@ -4437,7 +4437,7 @@
         <v>161</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
@@ -4670,7 +4670,7 @@
         <v>79</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>73</v>
@@ -5016,7 +5016,7 @@
         <v>75</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>210</v>
+        <v>817</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>71</v>
@@ -5032,7 +5032,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I75" s="7"/>
     </row>
@@ -5041,7 +5041,7 @@
         <v>76</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -5055,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I76" s="7"/>
     </row>
@@ -5064,7 +5064,7 @@
         <v>77</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>79</v>
@@ -5080,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I77" s="7"/>
     </row>
@@ -5089,7 +5089,7 @@
         <v>78</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>79</v>
@@ -5105,7 +5105,7 @@
         <v>1</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I78" s="7"/>
     </row>
@@ -5139,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
@@ -5153,7 +5153,7 @@
         <v>1</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I80" s="7"/>
     </row>
@@ -5162,7 +5162,7 @@
         <v>81</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>71</v>
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I81" s="7"/>
     </row>
@@ -5187,7 +5187,7 @@
         <v>82</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>79</v>
@@ -5203,7 +5203,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I82" s="7"/>
     </row>
@@ -5212,7 +5212,7 @@
         <v>83</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>79</v>
@@ -5228,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I83" s="7"/>
     </row>
@@ -5237,7 +5237,7 @@
         <v>84</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>28</v>
@@ -5253,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I84" s="7"/>
     </row>
@@ -5262,7 +5262,7 @@
         <v>85</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>63</v>
@@ -5278,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I85" s="7"/>
     </row>
@@ -5287,7 +5287,7 @@
         <v>86</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>63</v>
@@ -5303,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I86" s="7"/>
     </row>
@@ -5312,7 +5312,7 @@
         <v>87</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>63</v>
@@ -5328,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I87" s="7"/>
     </row>
@@ -5337,7 +5337,7 @@
         <v>88</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>98</v>
@@ -5353,7 +5353,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I88" s="7"/>
     </row>
@@ -5362,7 +5362,7 @@
         <v>89</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>98</v>
@@ -5378,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I89" s="7"/>
     </row>
@@ -5412,14 +5412,14 @@
         <v>91</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F91" s="4">
         <v>4</v>
@@ -5428,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I91" s="7"/>
     </row>
@@ -5437,14 +5437,14 @@
         <v>92</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F92" s="4">
         <v>4</v>
@@ -5453,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I92" s="7"/>
     </row>
@@ -5462,7 +5462,7 @@
         <v>93</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>63</v>
@@ -5478,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I93" s="7"/>
     </row>
@@ -5487,7 +5487,7 @@
         <v>94</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>63</v>
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I94" s="7"/>
     </row>
@@ -5512,7 +5512,7 @@
         <v>95</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>63</v>
@@ -5528,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I95" s="7"/>
     </row>
@@ -5537,7 +5537,7 @@
         <v>96</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>79</v>
@@ -5553,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I96" s="7"/>
     </row>
@@ -5562,7 +5562,7 @@
         <v>97</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>36</v>
@@ -5589,13 +5589,13 @@
         <v>98</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>79</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>73</v>
@@ -5616,7 +5616,7 @@
         <v>99</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>63</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I99" s="7"/>
     </row>
@@ -5641,7 +5641,7 @@
         <v>100</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>63</v>
@@ -5657,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I100" s="7"/>
     </row>
@@ -5666,7 +5666,7 @@
         <v>101</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>79</v>
@@ -5682,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I101" s="7"/>
     </row>
@@ -5691,13 +5691,13 @@
         <v>102</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>28</v>
@@ -5709,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I102" s="7"/>
     </row>
@@ -5718,7 +5718,7 @@
         <v>103</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -5732,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I103" s="7"/>
     </row>
@@ -5741,7 +5741,7 @@
         <v>104</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>63</v>
@@ -5757,7 +5757,7 @@
         <v>1</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I104" s="7"/>
     </row>
@@ -5766,7 +5766,7 @@
         <v>105</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>79</v>
@@ -5782,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I105" s="7"/>
     </row>
@@ -5791,7 +5791,7 @@
         <v>106</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>63</v>
@@ -5807,7 +5807,7 @@
         <v>1</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I106" s="7"/>
     </row>
@@ -5816,7 +5816,7 @@
         <v>107</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>63</v>
@@ -5832,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I107" s="7"/>
     </row>
@@ -5841,7 +5841,7 @@
         <v>108</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>98</v>
@@ -5857,7 +5857,7 @@
         <v>1</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I108" s="7"/>
     </row>
@@ -5866,7 +5866,7 @@
         <v>109</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>98</v>
@@ -5882,7 +5882,7 @@
         <v>1</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I109" s="7"/>
     </row>
@@ -5921,22 +5921,22 @@
         <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -5944,20 +5944,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C2" s="4">
         <v>186</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -5965,20 +5965,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C3" s="4">
         <v>178</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -5986,20 +5986,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C4" s="4">
         <v>88</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -6007,20 +6007,20 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C5" s="4">
         <v>64</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6028,7 +6028,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C6" s="4">
         <v>56</v>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -6049,20 +6049,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C7" s="4">
         <v>47</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -6070,20 +6070,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C8" s="4">
         <v>47</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -6091,7 +6091,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C9" s="4">
         <v>40</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -6112,7 +6112,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C10" s="4">
         <v>37</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -6133,7 +6133,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C11" s="4">
         <v>23</v>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -6161,7 +6161,7 @@
         <v>180</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="6"/>
@@ -6171,20 +6171,20 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C13" s="4">
         <v>17</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>293</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>294</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -6192,20 +6192,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="4">
         <v>16</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -6213,20 +6213,20 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C15" s="4">
         <v>16</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -6234,22 +6234,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C16" s="4">
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -6257,20 +6257,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C17" s="4">
         <v>15</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>293</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>294</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -6278,7 +6278,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C18" s="4">
         <v>14</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -6299,7 +6299,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C19" s="4">
         <v>13</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -6320,7 +6320,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C20" s="4">
         <v>13</v>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -6341,7 +6341,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C21" s="4">
         <v>13</v>
@@ -6356,7 +6356,7 @@
         <v>159</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -6364,7 +6364,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C22" s="4">
         <v>12</v>
@@ -6379,7 +6379,7 @@
         <v>159</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -6387,7 +6387,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C23" s="4">
         <v>10</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -6408,7 +6408,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C24" s="4">
         <v>9</v>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -6429,7 +6429,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C25" s="4">
         <v>9</v>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -6450,7 +6450,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C26" s="4">
         <v>9</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -6471,7 +6471,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C27" s="4">
         <v>9</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -6492,7 +6492,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C28" s="4">
         <v>9</v>
@@ -6501,13 +6501,13 @@
         <v>198</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -6515,7 +6515,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C29" s="4">
         <v>8</v>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -6536,7 +6536,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C30" s="4">
         <v>7</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -6557,7 +6557,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C31" s="4">
         <v>7</v>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -6578,22 +6578,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C32" s="4">
         <v>7</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>51</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -6601,20 +6601,20 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C33" s="4">
         <v>7</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -6622,20 +6622,20 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C34" s="4">
         <v>7</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -6643,7 +6643,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C35" s="4">
         <v>6</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -6664,7 +6664,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C36" s="4">
         <v>6</v>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -6685,7 +6685,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C37" s="4">
         <v>6</v>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -6706,7 +6706,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C38" s="4">
         <v>5</v>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -6727,7 +6727,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C39" s="4">
         <v>5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -6748,7 +6748,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C40" s="4">
         <v>5</v>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -6769,7 +6769,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C41" s="4">
         <v>5</v>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -6790,20 +6790,20 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C42" s="4">
         <v>5</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -6811,7 +6811,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C43" s="4">
         <v>5</v>
@@ -6826,7 +6826,7 @@
         <v>159</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -6834,7 +6834,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C44" s="4">
         <v>5</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -6855,22 +6855,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C45" s="4">
         <v>4</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -6878,20 +6878,20 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C46" s="4">
         <v>4</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -6899,7 +6899,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C47" s="4">
         <v>4</v>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -6920,22 +6920,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C48" s="4">
         <v>4</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -6943,7 +6943,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C49" s="4">
         <v>3</v>
@@ -6958,7 +6958,7 @@
         <v>159</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -6966,7 +6966,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C50" s="4">
         <v>3</v>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -6987,20 +6987,20 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C51" s="4">
         <v>3</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -7008,22 +7008,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -7031,7 +7031,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C53" s="4">
         <v>3</v>
@@ -7046,7 +7046,7 @@
         <v>159</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -7054,7 +7054,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C54" s="4">
         <v>3</v>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -7075,7 +7075,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C55" s="4">
         <v>3</v>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -7096,7 +7096,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C56" s="4">
         <v>3</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -7117,7 +7117,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C57" s="4">
         <v>3</v>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F57" s="8"/>
       <c r="G57" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -7138,7 +7138,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C58" s="4">
         <v>2</v>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -7159,7 +7159,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C59" s="4">
         <v>2</v>
@@ -7174,7 +7174,7 @@
         <v>37</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -7182,7 +7182,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C60" s="4">
         <v>2</v>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -7203,7 +7203,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C61" s="4">
         <v>2</v>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -7224,7 +7224,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C62" s="4">
         <v>2</v>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -7245,7 +7245,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C63" s="4">
         <v>2</v>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="F63" s="8"/>
       <c r="G63" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -7266,7 +7266,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C64" s="4">
         <v>2</v>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -7287,20 +7287,20 @@
         <v>64</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C65" s="4">
         <v>2</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -7308,7 +7308,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C66" s="4">
         <v>2</v>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -7329,7 +7329,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C67" s="4">
         <v>2</v>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -7350,7 +7350,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C68" s="4">
         <v>2</v>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -7371,20 +7371,20 @@
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F69" s="8"/>
       <c r="G69" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -7392,7 +7392,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C70" s="4">
         <v>2</v>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="F70" s="8"/>
       <c r="G70" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -7413,7 +7413,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C71" s="4">
         <v>2</v>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -7434,7 +7434,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C72" s="4">
         <v>2</v>
@@ -7449,7 +7449,7 @@
         <v>37</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -7457,20 +7457,20 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C73" s="4">
         <v>2</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -7478,7 +7478,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C74" s="4">
         <v>2</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -7499,7 +7499,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C75" s="4">
         <v>2</v>
@@ -7514,7 +7514,7 @@
         <v>159</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -7522,7 +7522,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C76" s="4">
         <v>2</v>
@@ -7537,7 +7537,7 @@
         <v>37</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -7545,20 +7545,20 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F77" s="8"/>
       <c r="G77" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -7566,7 +7566,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="F78" s="8"/>
       <c r="G78" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -7587,7 +7587,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C79" s="4">
         <v>2</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="F79" s="8"/>
       <c r="G79" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -7608,7 +7608,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C80" s="4">
         <v>1</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="F80" s="8"/>
       <c r="G80" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -7629,7 +7629,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C81" s="4">
         <v>1</v>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="F81" s="8"/>
       <c r="G81" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -7650,7 +7650,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C82" s="4">
         <v>1</v>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F82" s="8"/>
       <c r="G82" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -7671,7 +7671,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C83" s="4">
         <v>1</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="F83" s="8"/>
       <c r="G83" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -7692,7 +7692,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C84" s="4">
         <v>1</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -7713,7 +7713,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C85" s="4">
         <v>1</v>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F85" s="8"/>
       <c r="G85" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -7734,7 +7734,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C86" s="4">
         <v>1</v>
@@ -7747,7 +7747,7 @@
       </c>
       <c r="F86" s="8"/>
       <c r="G86" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -7755,7 +7755,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C87" s="4">
         <v>1</v>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="F87" s="8"/>
       <c r="G87" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -7776,7 +7776,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C88" s="4">
         <v>1</v>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F88" s="8"/>
       <c r="G88" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -7797,7 +7797,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C89" s="4">
         <v>1</v>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -7818,20 +7818,20 @@
         <v>89</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C90" s="4">
         <v>1</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -7839,22 +7839,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C91" s="4">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C91" s="4">
-        <v>1</v>
-      </c>
-      <c r="D91" s="4" t="s">
+      <c r="E91" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G91" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -7862,7 +7862,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C92" s="4">
         <v>1</v>
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F92" s="8"/>
       <c r="G92" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -7883,7 +7883,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C93" s="4">
         <v>1</v>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="F93" s="8"/>
       <c r="G93" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -7904,7 +7904,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C94" s="4">
         <v>1</v>
@@ -7917,7 +7917,7 @@
       </c>
       <c r="F94" s="8"/>
       <c r="G94" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -7925,7 +7925,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C95" s="4">
         <v>1</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="F95" s="8"/>
       <c r="G95" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -7946,22 +7946,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C96" s="4">
+        <v>1</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G96" s="6" t="s">
         <v>455</v>
-      </c>
-      <c r="C96" s="4">
-        <v>1</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -7969,7 +7969,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C97" s="4">
         <v>1</v>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="F97" s="8"/>
       <c r="G97" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -7990,7 +7990,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C98" s="4">
         <v>1</v>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -8011,7 +8011,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C99" s="4">
         <v>1</v>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="F99" s="8"/>
       <c r="G99" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -8032,7 +8032,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C100" s="4">
         <v>1</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="F100" s="8"/>
       <c r="G100" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -8053,20 +8053,20 @@
         <v>100</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C101" s="4">
         <v>1</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F101" s="8"/>
       <c r="G101" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -8074,7 +8074,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C102" s="4">
         <v>1</v>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="F102" s="8"/>
       <c r="G102" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -8095,7 +8095,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -8116,7 +8116,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C104" s="4">
         <v>1</v>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="F104" s="8"/>
       <c r="G104" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -8137,7 +8137,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C105" s="4">
         <v>1</v>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="F105" s="8"/>
       <c r="G105" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -8158,7 +8158,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C106" s="4">
         <v>1</v>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="F106" s="8"/>
       <c r="G106" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -8179,7 +8179,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C107" s="4">
         <v>1</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="F107" s="8"/>
       <c r="G107" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -8200,7 +8200,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C108" s="4">
         <v>1</v>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F108" s="8"/>
       <c r="G108" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -8221,7 +8221,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C109" s="4">
         <v>1</v>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="F109" s="8"/>
       <c r="G109" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -8242,7 +8242,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C110" s="4">
         <v>1</v>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="F110" s="8"/>
       <c r="G110" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -8263,7 +8263,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C111" s="4">
         <v>1</v>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="F111" s="8"/>
       <c r="G111" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -8284,7 +8284,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C112" s="4">
         <v>1</v>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="F112" s="8"/>
       <c r="G112" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -8305,20 +8305,20 @@
         <v>112</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C113" s="4">
         <v>1</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F113" s="8"/>
       <c r="G113" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -8326,22 +8326,22 @@
         <v>113</v>
       </c>
       <c r="B114" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C114" s="4">
+        <v>1</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G114" s="6" t="s">
         <v>490</v>
-      </c>
-      <c r="C114" s="4">
-        <v>1</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -8349,7 +8349,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C115" s="4">
         <v>1</v>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="F115" s="8"/>
       <c r="G115" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -8370,7 +8370,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C116" s="4">
         <v>1</v>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F116" s="8"/>
       <c r="G116" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -8391,7 +8391,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C117" s="4">
         <v>1</v>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="F117" s="8"/>
       <c r="G117" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -8412,7 +8412,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C118" s="4">
         <v>1</v>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="F118" s="8"/>
       <c r="G118" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -8433,7 +8433,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C119" s="4">
         <v>1</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="F119" s="8"/>
       <c r="G119" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -8454,7 +8454,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C120" s="4">
         <v>1</v>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="F120" s="8"/>
       <c r="G120" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -8475,7 +8475,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C121" s="4">
         <v>1</v>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="F121" s="8"/>
       <c r="G121" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -8496,7 +8496,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C122" s="4">
         <v>1</v>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="F122" s="8"/>
       <c r="G122" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -8517,7 +8517,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C123" s="4">
         <v>1</v>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="F123" s="8"/>
       <c r="G123" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -8538,7 +8538,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C124" s="4">
         <v>1</v>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="F124" s="8"/>
       <c r="G124" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -8559,7 +8559,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C125" s="4">
         <v>1</v>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -8580,7 +8580,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C126" s="4">
         <v>1</v>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="F126" s="8"/>
       <c r="G126" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -8601,20 +8601,20 @@
         <v>126</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C127" s="4">
         <v>1</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F127" s="8"/>
       <c r="G127" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -8622,7 +8622,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C128" s="4">
         <v>1</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F128" s="8"/>
       <c r="G128" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -8643,7 +8643,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C129" s="4">
         <v>1</v>
@@ -8658,7 +8658,7 @@
         <v>159</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -8666,7 +8666,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C130" s="4">
         <v>1</v>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="F130" s="8"/>
       <c r="G130" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -8687,7 +8687,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C131" s="4">
         <v>1</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="F131" s="8"/>
       <c r="G131" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -8708,7 +8708,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C132" s="4">
         <v>1</v>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="F132" s="8"/>
       <c r="G132" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -8729,7 +8729,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C133" s="4">
         <v>1</v>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F133" s="8"/>
       <c r="G133" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -8750,7 +8750,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C134" s="4">
         <v>1</v>
@@ -8773,7 +8773,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C135" s="4">
         <v>1</v>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F135" s="8"/>
       <c r="G135" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -8794,7 +8794,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C136" s="4">
         <v>1</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F136" s="8"/>
       <c r="G136" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -8815,7 +8815,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C137" s="4">
         <v>1</v>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="F137" s="8"/>
       <c r="G137" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -8836,7 +8836,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C138" s="4">
         <v>1</v>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="F138" s="8"/>
       <c r="G138" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -8857,22 +8857,22 @@
         <v>138</v>
       </c>
       <c r="B139" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C139" s="4">
+        <v>1</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G139" s="6" t="s">
         <v>539</v>
-      </c>
-      <c r="C139" s="4">
-        <v>1</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G139" s="6" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -8880,7 +8880,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C140" s="4">
         <v>1</v>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="F140" s="8"/>
       <c r="G140" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -8901,7 +8901,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C141" s="4">
         <v>1</v>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="F141" s="8"/>
       <c r="G141" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -8922,7 +8922,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C142" s="4">
         <v>1</v>
@@ -8937,7 +8937,7 @@
         <v>159</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -8945,7 +8945,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C143" s="4">
         <v>1</v>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="F143" s="8"/>
       <c r="G143" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8966,7 +8966,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C144" s="4">
         <v>1</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="F144" s="8"/>
       <c r="G144" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8987,7 +8987,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C145" s="4">
         <v>1</v>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="F145" s="8"/>
       <c r="G145" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -9008,7 +9008,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C146" s="4">
         <v>1</v>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F146" s="8"/>
       <c r="G146" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -9029,7 +9029,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C147" s="4">
         <v>1</v>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F147" s="8"/>
       <c r="G147" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -9050,7 +9050,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C148" s="4">
         <v>1</v>
@@ -9063,7 +9063,7 @@
       </c>
       <c r="F148" s="8"/>
       <c r="G148" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -9071,7 +9071,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C149" s="4">
         <v>1</v>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="F149" s="8"/>
       <c r="G149" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -9092,7 +9092,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C150" s="4">
         <v>1</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="F150" s="8"/>
       <c r="G150" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -9113,7 +9113,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C151" s="4">
         <v>1</v>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="F151" s="8"/>
       <c r="G151" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -9134,7 +9134,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C152" s="4">
         <v>1</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="F152" s="8"/>
       <c r="G152" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -9155,7 +9155,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C153" s="4">
         <v>1</v>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="F153" s="8"/>
       <c r="G153" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -9176,7 +9176,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C154" s="4">
         <v>1</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F154" s="8"/>
       <c r="G154" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
@@ -9197,7 +9197,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C155" s="4">
         <v>1</v>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="F155" s="8"/>
       <c r="G155" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -9218,7 +9218,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C156" s="4">
         <v>1</v>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="F156" s="8"/>
       <c r="G156" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -9239,7 +9239,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C157" s="4">
         <v>1</v>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="F157" s="8"/>
       <c r="G157" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -9260,7 +9260,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C158" s="4">
         <v>1</v>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="F158" s="8"/>
       <c r="G158" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -9281,7 +9281,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C159" s="4">
         <v>1</v>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="F159" s="8"/>
       <c r="G159" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -9302,7 +9302,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C160" s="4">
         <v>1</v>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="F160" s="8"/>
       <c r="G160" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -9323,7 +9323,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C161" s="4">
         <v>1</v>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="F161" s="8"/>
       <c r="G161" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -9344,20 +9344,20 @@
         <v>161</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C162" s="4">
         <v>1</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F162" s="8"/>
       <c r="G162" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
@@ -9365,7 +9365,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C163" s="4">
         <v>1</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="F163" s="8"/>
       <c r="G163" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
@@ -9386,7 +9386,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C164" s="4">
         <v>1</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="F164" s="8"/>
       <c r="G164" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -9407,20 +9407,20 @@
         <v>164</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C165" s="4">
         <v>1</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F165" s="8"/>
       <c r="G165" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
@@ -9428,7 +9428,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C166" s="4">
         <v>1</v>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F166" s="8"/>
       <c r="G166" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
@@ -9449,20 +9449,20 @@
         <v>166</v>
       </c>
       <c r="B167" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C167" s="4">
+        <v>1</v>
+      </c>
+      <c r="D167" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="C167" s="4">
-        <v>1</v>
-      </c>
-      <c r="D167" s="4" t="s">
+      <c r="E167" s="8" t="s">
         <v>593</v>
-      </c>
-      <c r="E167" s="8" t="s">
-        <v>594</v>
       </c>
       <c r="F167" s="8"/>
       <c r="G167" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
@@ -9470,20 +9470,20 @@
         <v>167</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C168" s="4">
         <v>1</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E168" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F168" s="8"/>
       <c r="G168" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
@@ -9491,7 +9491,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C169" s="4">
         <v>1</v>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="F169" s="8"/>
       <c r="G169" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
@@ -9512,7 +9512,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C170" s="4">
         <v>1</v>
@@ -9525,7 +9525,7 @@
       </c>
       <c r="F170" s="8"/>
       <c r="G170" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -9533,7 +9533,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C171" s="4">
         <v>1</v>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F171" s="8"/>
       <c r="G171" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
@@ -9554,7 +9554,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C172" s="4">
         <v>1</v>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="F172" s="8"/>
       <c r="G172" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
@@ -9575,7 +9575,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C173" s="4">
         <v>1</v>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="F173" s="8"/>
       <c r="G173" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
@@ -9596,7 +9596,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C174" s="4">
         <v>1</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="F174" s="8"/>
       <c r="G174" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
@@ -9617,7 +9617,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C175" s="4">
         <v>1</v>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="F175" s="8"/>
       <c r="G175" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
@@ -9638,7 +9638,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C176" s="4">
         <v>1</v>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="F176" s="8"/>
       <c r="G176" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
@@ -9659,7 +9659,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C177" s="4">
         <v>1</v>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F177" s="8"/>
       <c r="G177" s="6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
@@ -9680,7 +9680,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C178" s="4">
         <v>1</v>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="F178" s="8"/>
       <c r="G178" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
@@ -9701,7 +9701,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C179" s="4">
         <v>1</v>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F179" s="8"/>
       <c r="G179" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
@@ -9722,7 +9722,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C180" s="4">
         <v>1</v>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="F180" s="8"/>
       <c r="G180" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
@@ -9743,22 +9743,22 @@
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="C181" s="4">
+        <v>1</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G181" s="6" t="s">
         <v>613</v>
-      </c>
-      <c r="C181" s="4">
-        <v>1</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E181" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F181" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
@@ -9766,7 +9766,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C182" s="4">
         <v>1</v>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="F182" s="8"/>
       <c r="G182" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
@@ -9787,7 +9787,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C183" s="4">
         <v>1</v>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F183" s="8"/>
       <c r="G183" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
@@ -9808,20 +9808,20 @@
         <v>183</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C184" s="4">
         <v>1</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F184" s="8"/>
       <c r="G184" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -9829,20 +9829,20 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C185" s="4">
         <v>1</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E185" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F185" s="8"/>
       <c r="G185" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
@@ -9850,7 +9850,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C186" s="4">
         <v>1</v>
@@ -9863,7 +9863,7 @@
       </c>
       <c r="F186" s="8"/>
       <c r="G186" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
@@ -9871,7 +9871,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C187" s="4">
         <v>1</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="F187" s="8"/>
       <c r="G187" s="6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
@@ -9892,7 +9892,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C188" s="4">
         <v>1</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="F188" s="8"/>
       <c r="G188" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
@@ -9913,7 +9913,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C189" s="4">
         <v>1</v>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="F189" s="8"/>
       <c r="G189" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,7 +9934,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C190" s="4">
         <v>1</v>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="F190" s="8"/>
       <c r="G190" s="6" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -9955,7 +9955,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C191" s="4">
         <v>1</v>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="F191" s="8"/>
       <c r="G191" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
@@ -9976,7 +9976,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C192" s="4">
         <v>1</v>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="F192" s="8"/>
       <c r="G192" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -9997,22 +9997,22 @@
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="C193" s="4">
+        <v>1</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G193" s="6" t="s">
         <v>637</v>
-      </c>
-      <c r="C193" s="4">
-        <v>1</v>
-      </c>
-      <c r="D193" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E193" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F193" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G193" s="6" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -10020,7 +10020,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C194" s="4">
         <v>1</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="F194" s="8"/>
       <c r="G194" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -10041,7 +10041,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C195" s="4">
         <v>1</v>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F195" s="8"/>
       <c r="G195" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -10062,7 +10062,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C196" s="4">
         <v>1</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F196" s="8"/>
       <c r="G196" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -10083,7 +10083,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C197" s="4">
         <v>1</v>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F197" s="8"/>
       <c r="G197" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -10104,7 +10104,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C198" s="4">
         <v>1</v>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="F198" s="8"/>
       <c r="G198" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -10125,7 +10125,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C199" s="4">
         <v>1</v>
@@ -10134,13 +10134,13 @@
         <v>198</v>
       </c>
       <c r="E199" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F199" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G199" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -10148,7 +10148,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C200" s="4">
         <v>1</v>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="F200" s="8"/>
       <c r="G200" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
@@ -10169,7 +10169,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C201" s="4">
         <v>1</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F201" s="8"/>
       <c r="G201" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
@@ -10190,7 +10190,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C202" s="4">
         <v>1</v>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="F202" s="8"/>
       <c r="G202" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -10211,7 +10211,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C203" s="4">
         <v>1</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="F203" s="8"/>
       <c r="G203" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
@@ -10232,7 +10232,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C204" s="4">
         <v>1</v>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="F204" s="8"/>
       <c r="G204" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
@@ -10253,7 +10253,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C205" s="4">
         <v>1</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="F205" s="8"/>
       <c r="G205" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
@@ -10274,7 +10274,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C206" s="4">
         <v>1</v>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="F206" s="8"/>
       <c r="G206" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
@@ -10295,7 +10295,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C207" s="4">
         <v>1</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="F207" s="8"/>
       <c r="G207" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
@@ -10316,7 +10316,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C208" s="4">
         <v>1</v>
@@ -10331,7 +10331,7 @@
         <v>159</v>
       </c>
       <c r="G208" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
@@ -10339,7 +10339,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C209" s="4">
         <v>1</v>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="F209" s="8"/>
       <c r="G209" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -10360,7 +10360,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C210" s="4">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>159</v>
       </c>
       <c r="G210" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
@@ -10383,7 +10383,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C211" s="4">
         <v>1</v>
@@ -10398,7 +10398,7 @@
         <v>159</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
@@ -10406,7 +10406,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C212" s="4">
         <v>1</v>
@@ -10421,7 +10421,7 @@
         <v>159</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
@@ -10429,7 +10429,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C213" s="4">
         <v>1</v>
@@ -10444,7 +10444,7 @@
         <v>159</v>
       </c>
       <c r="G213" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
@@ -10452,7 +10452,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C214" s="4">
         <v>1</v>
@@ -10467,7 +10467,7 @@
         <v>159</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
@@ -10475,7 +10475,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C215" s="4">
         <v>1</v>
@@ -10490,7 +10490,7 @@
         <v>159</v>
       </c>
       <c r="G215" s="6" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -10498,7 +10498,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C216" s="4">
         <v>1</v>
@@ -10513,7 +10513,7 @@
         <v>159</v>
       </c>
       <c r="G216" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -10521,22 +10521,22 @@
         <v>216</v>
       </c>
       <c r="B217" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="C217" s="4">
+        <v>1</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G217" s="6" t="s">
         <v>684</v>
-      </c>
-      <c r="C217" s="4">
-        <v>1</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E217" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F217" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G217" s="6" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -10544,7 +10544,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C218" s="4">
         <v>1</v>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="F218" s="8"/>
       <c r="G218" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -10565,7 +10565,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C219" s="4">
         <v>1</v>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="F219" s="8"/>
       <c r="G219" s="6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -10586,7 +10586,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C220" s="4">
         <v>1</v>
@@ -10601,7 +10601,7 @@
         <v>159</v>
       </c>
       <c r="G220" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -10609,7 +10609,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C221" s="4">
         <v>1</v>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="F221" s="8"/>
       <c r="G221" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -10630,7 +10630,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C222" s="4">
         <v>1</v>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F222" s="8"/>
       <c r="G222" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -10651,7 +10651,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C223" s="4">
         <v>1</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F223" s="8"/>
       <c r="G223" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -10672,7 +10672,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C224" s="4">
         <v>1</v>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="F224" s="8"/>
       <c r="G224" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,7 +10693,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C225" s="4">
         <v>1</v>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="F225" s="8"/>
       <c r="G225" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -10714,22 +10714,22 @@
         <v>225</v>
       </c>
       <c r="B226" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="C226" s="4">
+        <v>1</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="E226" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F226" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G226" s="6" t="s">
         <v>702</v>
-      </c>
-      <c r="C226" s="4">
-        <v>1</v>
-      </c>
-      <c r="D226" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E226" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="F226" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="G226" s="6" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -10737,7 +10737,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C227" s="4">
         <v>1</v>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="F227" s="8"/>
       <c r="G227" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -10758,7 +10758,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C228" s="4">
         <v>1</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="F228" s="8"/>
       <c r="G228" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -10779,7 +10779,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C229" s="4">
         <v>1</v>
@@ -10792,7 +10792,7 @@
       </c>
       <c r="F229" s="8"/>
       <c r="G229" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -10800,7 +10800,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C230" s="4">
         <v>1</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="F230" s="8"/>
       <c r="G230" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10821,7 +10821,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C231" s="4">
         <v>1</v>
@@ -10834,7 +10834,7 @@
       </c>
       <c r="F231" s="8"/>
       <c r="G231" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10842,7 +10842,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C232" s="4">
         <v>1</v>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="F232" s="8"/>
       <c r="G232" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10863,7 +10863,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C233" s="4">
         <v>1</v>
@@ -10876,7 +10876,7 @@
       </c>
       <c r="F233" s="8"/>
       <c r="G233" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10884,7 +10884,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C234" s="4">
         <v>1</v>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="F234" s="8"/>
       <c r="G234" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10905,7 +10905,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C235" s="4">
         <v>1</v>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="F235" s="8"/>
       <c r="G235" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10926,7 +10926,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C236" s="4">
         <v>1</v>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="F236" s="8"/>
       <c r="G236" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10947,7 +10947,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C237" s="4">
         <v>1</v>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="F237" s="8"/>
       <c r="G237" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10968,7 +10968,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C238" s="4">
         <v>1</v>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="F238" s="8"/>
       <c r="G238" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10989,7 +10989,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C239" s="4">
         <v>1</v>
@@ -11002,7 +11002,7 @@
       </c>
       <c r="F239" s="8"/>
       <c r="G239" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -11010,7 +11010,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C240" s="4">
         <v>1</v>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="F240" s="8"/>
       <c r="G240" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -11031,7 +11031,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C241" s="4">
         <v>1</v>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="F241" s="8"/>
       <c r="G241" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -11052,7 +11052,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C242" s="4">
         <v>1</v>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F242" s="8"/>
       <c r="G242" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -11073,7 +11073,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C243" s="4">
         <v>1</v>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="F243" s="8"/>
       <c r="G243" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -11094,7 +11094,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C244" s="4">
         <v>1</v>
@@ -11103,13 +11103,13 @@
         <v>198</v>
       </c>
       <c r="E244" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F244" s="8" t="s">
         <v>198</v>
       </c>
       <c r="G244" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -11117,7 +11117,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C245" s="4">
         <v>1</v>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="F245" s="8"/>
       <c r="G245" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -11138,7 +11138,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C246" s="4">
         <v>1</v>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="F246" s="8"/>
       <c r="G246" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -11159,7 +11159,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C247" s="4">
         <v>1</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="F247" s="8"/>
       <c r="G247" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -11180,7 +11180,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C248" s="4">
         <v>1</v>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F248" s="8"/>
       <c r="G248" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -11201,7 +11201,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C249" s="4">
         <v>1</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F249" s="8"/>
       <c r="G249" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,7 +11222,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C250" s="4">
         <v>1</v>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F250" s="8"/>
       <c r="G250" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -11243,7 +11243,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C251" s="4">
         <v>1</v>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="F251" s="8"/>
       <c r="G251" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -11264,7 +11264,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C252" s="4">
         <v>1</v>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="F252" s="8"/>
       <c r="G252" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -11285,20 +11285,20 @@
         <v>252</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C253" s="4">
         <v>1</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F253" s="8"/>
       <c r="G253" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -11306,7 +11306,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C254" s="4">
         <v>1</v>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="F254" s="8"/>
       <c r="G254" s="6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -11327,7 +11327,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C255" s="4">
         <v>1</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F255" s="8"/>
       <c r="G255" s="6" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -11348,7 +11348,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C256" s="4">
         <v>1</v>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="F256" s="8"/>
       <c r="G256" s="6" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -11369,7 +11369,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C257" s="4">
         <v>1</v>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="F257" s="8"/>
       <c r="G257" s="6" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -11390,7 +11390,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C258" s="4">
         <v>1</v>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="F258" s="8"/>
       <c r="G258" s="6" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -11411,7 +11411,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C259" s="4">
         <v>1</v>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="F259" s="8"/>
       <c r="G259" s="6" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -11432,7 +11432,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C260" s="4">
         <v>1</v>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="F260" s="8"/>
       <c r="G260" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -11453,7 +11453,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C261" s="4">
         <v>1</v>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F261" s="8"/>
       <c r="G261" s="6" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -11474,20 +11474,20 @@
         <v>261</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C262" s="4">
         <v>1</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F262" s="8"/>
       <c r="G262" s="6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -11495,7 +11495,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C263" s="4">
         <v>1</v>
@@ -11508,7 +11508,7 @@
       </c>
       <c r="F263" s="8"/>
       <c r="G263" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -11516,20 +11516,20 @@
         <v>263</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C264" s="4">
         <v>1</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E264" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F264" s="8"/>
       <c r="G264" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -11537,7 +11537,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C265" s="4">
         <v>1</v>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="F265" s="8"/>
       <c r="G265" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -11558,7 +11558,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C266" s="4">
         <v>1</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F266" s="8"/>
       <c r="G266" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -11579,7 +11579,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C267" s="4">
         <v>1</v>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="F267" s="8"/>
       <c r="G267" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -11600,7 +11600,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C268" s="4">
         <v>1</v>
@@ -11613,7 +11613,7 @@
       </c>
       <c r="F268" s="8"/>
       <c r="G268" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -11621,7 +11621,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C269" s="4">
         <v>1</v>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="F269" s="8"/>
       <c r="G269" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -11642,7 +11642,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C270" s="4">
         <v>1</v>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="F270" s="8"/>
       <c r="G270" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -11663,7 +11663,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C271" s="4">
         <v>1</v>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F271" s="8"/>
       <c r="G271" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -11684,7 +11684,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C272" s="4">
         <v>1</v>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="F272" s="8"/>
       <c r="G272" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,7 +11705,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C273" s="4">
         <v>1</v>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="F273" s="8"/>
       <c r="G273" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -11773,7 +11773,7 @@
         <v>20</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -11781,7 +11781,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -11789,7 +11789,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -11797,23 +11797,23 @@
         <v>150</v>
       </c>
       <c r="B4" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B5" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -11821,15 +11821,15 @@
         <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
+        <v>794</v>
+      </c>
+      <c r="B8" t="s">
         <v>795</v>
-      </c>
-      <c r="B8" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -11837,7 +11837,7 @@
         <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -11845,7 +11845,7 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -11853,15 +11853,15 @@
         <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -11869,15 +11869,15 @@
         <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
+        <v>798</v>
+      </c>
+      <c r="B14" t="s">
         <v>799</v>
-      </c>
-      <c r="B14" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -11893,15 +11893,15 @@
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="B17" t="s">
         <v>802</v>
-      </c>
-      <c r="B17" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -11909,15 +11909,15 @@
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
+        <v>804</v>
+      </c>
+      <c r="B19" t="s">
         <v>805</v>
-      </c>
-      <c r="B19" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -11925,71 +11925,71 @@
         <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B21" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B22" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B23" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B24" t="s">
         <v>809</v>
-      </c>
-      <c r="B24" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B25" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B27" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B28" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AECD1C5-6427-40C6-93F9-F5614CE66D29}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEEBA728-AE70-4D73-8C1E-8A792ADB9FC7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1613,7 +1613,7 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="8" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>18</v>

--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="297" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEEBA728-AE70-4D73-8C1E-8A792ADB9FC7}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11356409-6F81-4556-BEA6-D8FBCD599814}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="226">
   <si>
     <t>Patrón texto</t>
   </si>
@@ -382,15 +382,6 @@
   </si>
   <si>
     <t>Bebé</t>
-  </si>
-  <si>
-    <t>Mapfre</t>
-  </si>
-  <si>
-    <t>Casa · Auto · Otro</t>
-  </si>
-  <si>
-    <t>Bonus</t>
   </si>
   <si>
     <t>Farmacia · Dentista · BCBS · Médico · Estudios · Otro</t>
@@ -1359,15 +1350,15 @@
         <v>77</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1378,15 +1369,15 @@
         <v>43</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1394,13 +1385,13 @@
         <v>36</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1410,14 +1401,14 @@
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1431,15 +1422,15 @@
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1450,15 +1441,15 @@
         <v>62</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1469,15 +1460,15 @@
         <v>73</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1488,10 +1479,10 @@
         <v>43</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1505,15 +1496,15 @@
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1524,15 +1515,15 @@
         <v>72</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1540,13 +1531,13 @@
         <v>61</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1562,10 +1553,10 @@
         <v>64</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1581,10 +1572,10 @@
         <v>27</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1597,13 +1588,13 @@
         <v>61</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1619,15 +1610,15 @@
         <v>18</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1635,13 +1626,13 @@
         <v>39</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1654,13 +1645,13 @@
         <v>36</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1673,13 +1664,13 @@
         <v>45</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1695,10 +1686,10 @@
         <v>66</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1712,29 +1703,29 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1750,15 +1741,15 @@
         <v>80</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1767,10 +1758,10 @@
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1784,16 +1775,16 @@
         <v>1500</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1807,16 +1798,16 @@
         <v>5000</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E26" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>180</v>
-      </c>
       <c r="G26" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1829,13 +1820,13 @@
         <v>36</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1845,16 +1836,16 @@
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1864,16 +1855,16 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1883,21 +1874,21 @@
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1905,32 +1896,32 @@
         <v>36</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1940,16 +1931,16 @@
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1965,15 +1956,15 @@
         <v>71</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -1981,13 +1972,13 @@
         <v>41</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2003,15 +1994,15 @@
         <v>48</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -2022,15 +2013,15 @@
         <v>27</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -2038,13 +2029,13 @@
         <v>8</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2057,18 +2048,18 @@
         <v>8</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -2076,18 +2067,18 @@
         <v>52</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -2095,18 +2086,18 @@
         <v>61</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2117,10 +2108,10 @@
         <v>27</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2136,15 +2127,15 @@
         <v>27</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -2152,13 +2143,13 @@
         <v>36</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2172,10 +2163,10 @@
       </c>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2191,10 +2182,10 @@
         <v>27</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2210,15 +2201,15 @@
         <v>31</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -2229,10 +2220,10 @@
         <v>57</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2248,29 +2239,29 @@
         <v>57</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="8" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2283,13 +2274,13 @@
         <v>11</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2302,32 +2293,32 @@
         <v>52</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2343,10 +2334,10 @@
         <v>69</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2362,48 +2353,48 @@
         <v>27</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2419,15 +2410,15 @@
         <v>75</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -2435,13 +2426,13 @@
         <v>8</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2454,18 +2445,18 @@
         <v>52</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -2473,13 +2464,13 @@
         <v>52</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2498,13 +2489,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una categoría de la lista de la hoja Categorías" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
-            <xm:f>Categorías!$A$2:$A$28</xm:f>
+            <xm:f>Categorías!$A$2:$A$27</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D686</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
-            <xm:f>Categorías!$D$2:$D$63</xm:f>
+            <xm:f>Categorías!$D$2:$D$62</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E686</xm:sqref>
         </x14:dataValidation>
@@ -2516,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2603,117 +2594,117 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
         <v>126</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" t="s">
         <v>132</v>
-      </c>
-      <c r="B17" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s">
         <v>134</v>
@@ -2724,54 +2715,54 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" t="s">
         <v>136</v>
-      </c>
-      <c r="B19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>139</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="B21" t="s">
         <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B22" t="s">
         <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" t="s">
         <v>141</v>
-      </c>
-      <c r="B23" t="s">
-        <v>114</v>
       </c>
       <c r="D23" t="s">
         <v>142</v>
@@ -2782,229 +2773,218 @@
         <v>143</v>
       </c>
       <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
         <v>144</v>
-      </c>
-      <c r="D24" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
         <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
         <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>75</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>15</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>157</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>159</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>165</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>51</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D63" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11356409-6F81-4556-BEA6-D8FBCD599814}"/>
+  <xr:revisionPtr revIDLastSave="306" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A0F224-6AF9-4C47-B7BF-0CEC041DCCD5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="228">
   <si>
     <t>Patrón texto</t>
   </si>
@@ -186,9 +186,6 @@
     <t>Social / Amigos</t>
   </si>
   <si>
-    <t>MISTERIO</t>
-  </si>
-  <si>
     <t>CAFE VD</t>
   </si>
   <si>
@@ -703,6 +700,15 @@
   </si>
   <si>
     <t>Dona Coxinha</t>
+  </si>
+  <si>
+    <t>Milanesas</t>
+  </si>
+  <si>
+    <t>Rudy</t>
+  </si>
+  <si>
+    <t>MISTERI</t>
   </si>
 </sst>
 </file>
@@ -769,7 +775,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -792,11 +798,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E7EB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -813,6 +830,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1127,7 +1145,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1135,7 +1153,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
@@ -1143,17 +1161,17 @@
     </row>
     <row r="5" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
@@ -1161,7 +1179,7 @@
     </row>
     <row r="9" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
@@ -1169,17 +1187,17 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
@@ -1187,12 +1205,12 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
@@ -1200,12 +1218,12 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
@@ -1213,12 +1231,12 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
@@ -1226,7 +1244,7 @@
     </row>
     <row r="24" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
@@ -1234,12 +1252,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
@@ -1247,22 +1265,22 @@
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
@@ -1270,12 +1288,12 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
@@ -1283,17 +1301,17 @@
     </row>
     <row r="37" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1303,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1339,26 +1357,26 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1369,15 +1387,15 @@
         <v>43</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1385,13 +1403,13 @@
         <v>36</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1401,74 +1419,76 @@
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>226</v>
+      </c>
       <c r="F6" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1479,10 +1499,10 @@
         <v>43</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1496,67 +1516,67 @@
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1572,29 +1592,29 @@
         <v>27</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1610,15 +1630,15 @@
         <v>18</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1626,13 +1646,13 @@
         <v>39</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1645,13 +1665,13 @@
         <v>36</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1664,37 +1684,37 @@
         <v>45</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1703,53 +1723,53 @@
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1758,10 +1778,10 @@
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1775,16 +1795,16 @@
         <v>1500</v>
       </c>
       <c r="D25" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>173</v>
-      </c>
       <c r="F25" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1798,16 +1818,16 @@
         <v>5000</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1820,13 +1840,13 @@
         <v>36</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1836,16 +1856,16 @@
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1855,16 +1875,16 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1874,21 +1894,21 @@
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E30" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>177</v>
-      </c>
       <c r="G30" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1896,32 +1916,32 @@
         <v>36</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
       <c r="D32" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1931,40 +1951,40 @@
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
@@ -1972,13 +1992,13 @@
         <v>41</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1994,15 +2014,15 @@
         <v>48</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -2013,15 +2033,15 @@
         <v>27</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -2029,13 +2049,13 @@
         <v>8</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2048,18 +2068,18 @@
         <v>8</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
@@ -2067,37 +2087,37 @@
         <v>52</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2108,10 +2128,10 @@
         <v>27</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2127,15 +2147,15 @@
         <v>27</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
@@ -2143,13 +2163,13 @@
         <v>36</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2163,10 +2183,10 @@
       </c>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2182,10 +2202,10 @@
         <v>27</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2201,15 +2221,15 @@
         <v>31</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -2217,18 +2237,18 @@
         <v>52</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -2236,32 +2256,32 @@
         <v>52</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2274,18 +2294,18 @@
         <v>11</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -2293,51 +2313,51 @@
         <v>52</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2353,72 +2373,72 @@
         <v>27</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
       <c r="D56" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
@@ -2426,18 +2446,18 @@
         <v>8</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -2445,18 +2465,18 @@
         <v>52</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -2464,13 +2484,30 @@
         <v>52</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>3481838</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2520,18 +2557,18 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
         <v>48</v>
@@ -2542,10 +2579,10 @@
         <v>45</v>
       </c>
       <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
         <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -2553,10 +2590,10 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" t="s">
         <v>114</v>
-      </c>
-      <c r="D4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -2564,21 +2601,21 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" t="s">
         <v>117</v>
-      </c>
-      <c r="B6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -2586,10 +2623,10 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -2597,7 +2634,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
@@ -2608,10 +2645,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -2619,10 +2656,10 @@
         <v>26</v>
       </c>
       <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" t="s">
         <v>120</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -2630,10 +2667,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -2641,18 +2678,18 @@
         <v>52</v>
       </c>
       <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
         <v>123</v>
-      </c>
-      <c r="D12" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s">
         <v>125</v>
-      </c>
-      <c r="B13" t="s">
-        <v>126</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -2666,7 +2703,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -2674,18 +2711,18 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" t="s">
         <v>129</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
@@ -2696,21 +2733,21 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" t="s">
         <v>131</v>
-      </c>
-      <c r="D17" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" t="s">
         <v>133</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>134</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2718,18 +2755,18 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
         <v>42</v>
@@ -2737,46 +2774,46 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" t="s">
         <v>138</v>
-      </c>
-      <c r="B22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
         <v>140</v>
       </c>
-      <c r="B23" t="s">
+      <c r="D23" t="s">
         <v>141</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
         <v>143</v>
-      </c>
-      <c r="B24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2784,32 +2821,32 @@
         <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s">
         <v>146</v>
-      </c>
-      <c r="B26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -2824,17 +2861,17 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.3">
@@ -2849,42 +2886,42 @@
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.3">
@@ -2894,22 +2931,22 @@
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.3">
@@ -2929,47 +2966,47 @@
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.3">
@@ -2979,12 +3016,12 @@
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="62" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="306" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3A0F224-6AF9-4C47-B7BF-0CEC041DCCD5}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13B123BA-98BF-4A09-8C35-0A85DC818885}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="229">
   <si>
     <t>Patrón texto</t>
   </si>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>MISTERI</t>
+  </si>
+  <si>
+    <t>TIENDA INLGE</t>
   </si>
 </sst>
 </file>
@@ -813,7 +816,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -830,7 +833,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1321,7 +1327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2508,6 +2514,17 @@
       </c>
       <c r="G62" s="12" t="s">
         <v>177</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13B123BA-98BF-4A09-8C35-0A85DC818885}"/>
+  <xr:revisionPtr revIDLastSave="333" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932CB609-2C98-4018-835A-1FD9E36CBEE6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reglas!$A$1:$G$61</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="235">
   <si>
     <t>Patrón texto</t>
   </si>
@@ -712,6 +725,24 @@
   </si>
   <si>
     <t>TIENDA INLGE</t>
+  </si>
+  <si>
+    <t>CAMBIOST</t>
+  </si>
+  <si>
+    <t>Jardinero</t>
+  </si>
+  <si>
+    <t>MOVIE</t>
+  </si>
+  <si>
+    <t>RIOGAS</t>
+  </si>
+  <si>
+    <t>Garrafa</t>
+  </si>
+  <si>
+    <t>Uruing</t>
   </si>
 </sst>
 </file>
@@ -816,7 +847,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -834,9 +865,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1327,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2525,6 +2560,84 @@
       </c>
       <c r="E63" s="9" t="s">
         <v>71</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G63" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64">
+        <v>1200</v>
+      </c>
+      <c r="C64">
+        <v>1200</v>
+      </c>
+      <c r="D64" t="s">
+        <v>230</v>
+      </c>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G64" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E65" t="s">
+        <v>54</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="D66" t="s">
+        <v>36</v>
+      </c>
+      <c r="E66" t="s">
+        <v>233</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1935968</v>
+      </c>
+      <c r="D67" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" t="s">
+        <v>234</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/mapping_propuesto.xlsx
+++ b/mapping_propuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cd914253cd8ed602/EMPRESAS/Python Devs/finanzas-familia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="333" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932CB609-2C98-4018-835A-1FD9E36CBEE6}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="11_D4AC3F2485E13763C1D08F2EA23E4392933AA06F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D4D0259-A2C9-4B09-BB33-A9F76F706174}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Categorías" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reglas!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Reglas!$A$1:$G$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="236">
   <si>
     <t>Patrón texto</t>
   </si>
@@ -583,9 +583,6 @@
     <t>Ingresos</t>
   </si>
   <si>
-    <t>DEB. VARIOS VISA-ILINK</t>
-  </si>
-  <si>
     <t>S.E.M.M.</t>
   </si>
   <si>
@@ -743,6 +740,12 @@
   </si>
   <si>
     <t>Uruing</t>
+  </si>
+  <si>
+    <t>C.J.P.P</t>
+  </si>
+  <si>
+    <t>SEGURO DE VIDA</t>
   </si>
 </sst>
 </file>
@@ -847,7 +850,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -868,10 +871,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1362,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1417,7 +1416,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1480,7 +1479,7 @@
         <v>52</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>179</v>
@@ -1491,7 +1490,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -1510,7 +1509,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1529,7 +1528,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1565,7 +1564,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -1584,7 +1583,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1592,7 +1591,7 @@
         <v>60</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>179</v>
@@ -1649,7 +1648,7 @@
         <v>60</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>179</v>
@@ -1679,7 +1678,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1687,7 +1686,7 @@
         <v>39</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>179</v>
@@ -1706,7 +1705,7 @@
         <v>36</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>179</v>
@@ -1725,7 +1724,7 @@
         <v>45</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>179</v>
@@ -1772,7 +1771,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1780,7 +1779,7 @@
         <v>132</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>179</v>
@@ -1809,17 +1808,23 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>181</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="7">
+        <v>800</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1500</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>172</v>
+      </c>
       <c r="F24" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>177</v>
@@ -1830,16 +1835,16 @@
         <v>16</v>
       </c>
       <c r="B25" s="7">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="C25" s="7">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>171</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>176</v>
@@ -1850,19 +1855,15 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="7">
-        <v>4000</v>
-      </c>
-      <c r="C26" s="7">
-        <v>5000</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>171</v>
+        <v>12</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>176</v>
@@ -1873,15 +1874,15 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="8" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>176</v>
@@ -1892,7 +1893,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -1900,7 +1901,7 @@
         <v>170</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>176</v>
@@ -1911,7 +1912,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1919,7 +1920,7 @@
         <v>170</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>176</v>
@@ -1930,15 +1931,15 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="8" t="s">
-        <v>170</v>
+        <v>36</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>176</v>
@@ -1949,15 +1950,15 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="8" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>176</v>
@@ -1968,7 +1969,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1976,7 +1977,7 @@
         <v>170</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>176</v>
@@ -1987,18 +1988,18 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
       <c r="D33" s="8" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>177</v>
@@ -2006,18 +2007,18 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>69</v>
+        <v>181</v>
       </c>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
       <c r="D34" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>177</v>
@@ -2025,18 +2026,18 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
       <c r="D35" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>177</v>
@@ -2044,15 +2045,15 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="8" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>179</v>
@@ -2068,10 +2069,10 @@
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="8" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>27</v>
+        <v>223</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>179</v>
@@ -2082,7 +2083,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
-        <v>202</v>
+        <v>9</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -2090,7 +2091,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>179</v>
@@ -2101,15 +2102,15 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
       <c r="D39" s="8" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>179</v>
@@ -2120,15 +2121,15 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="7"/>
       <c r="D40" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>204</v>
+        <v>138</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>179</v>
@@ -2144,10 +2145,10 @@
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
       <c r="D41" s="8" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>179</v>
@@ -2158,7 +2159,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="7"/>
@@ -2177,15 +2178,15 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
-        <v>28</v>
+        <v>206</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="8" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>179</v>
@@ -2196,16 +2197,14 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>207</v>
+        <v>34</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>208</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
         <v>179</v>
       </c>
@@ -2215,14 +2214,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="9"/>
+        <v>26</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="F45" s="9" t="s">
         <v>179</v>
       </c>
@@ -2232,18 +2233,18 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
       <c r="D46" s="8" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>177</v>
@@ -2251,7 +2252,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>30</v>
+        <v>208</v>
       </c>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
@@ -2259,7 +2260,7 @@
         <v>52</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>179</v>
@@ -2270,7 +2271,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -2289,15 +2290,15 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
-        <v>59</v>
+        <v>209</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
       <c r="D49" s="8" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>179</v>
@@ -2308,18 +2309,18 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
-        <v>210</v>
+        <v>13</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
       <c r="D50" s="8" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>211</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G50" s="9" t="s">
         <v>177</v>
@@ -2327,18 +2328,18 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
-        <v>13</v>
+        <v>226</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
       <c r="D51" s="8" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>212</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>177</v>
@@ -2346,18 +2347,18 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="8" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>177</v>
@@ -2365,18 +2366,18 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>214</v>
+        <v>67</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
       <c r="D53" s="8" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>177</v>
@@ -2384,15 +2385,15 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="8" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>179</v>
@@ -2403,18 +2404,18 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>32</v>
+        <v>215</v>
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="8" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>27</v>
+        <v>216</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>177</v>
@@ -2422,7 +2423,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -2430,7 +2431,7 @@
         <v>170</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>176</v>
@@ -2441,18 +2442,18 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="7"/>
       <c r="D57" s="8" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>177</v>
@@ -2460,15 +2461,15 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
       <c r="D58" s="8" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>179</v>
@@ -2479,12 +2480,12 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>218</v>
+        <v>55</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="7"/>
       <c r="D59" s="8" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -2498,7 +2499,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -2506,7 +2507,7 @@
         <v>52</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>179</v>
@@ -2516,33 +2517,31 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
+      <c r="A61">
+        <v>3481838</v>
+      </c>
       <c r="D61" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="G61" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G61" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>3481838</v>
+      <c r="A62" s="13" t="s">
+        <v>227</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E62" s="12" t="s">
-        <v>225</v>
+      <c r="E62" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>179</v>
@@ -2555,12 +2554,16 @@
       <c r="A63" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="D63" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>71</v>
-      </c>
+      <c r="B63">
+        <v>1200</v>
+      </c>
+      <c r="C63">
+        <v>1200</v>
+      </c>
+      <c r="D63" t="s">
+        <v>229</v>
+      </c>
+      <c r="E63" s="12"/>
       <c r="F63" s="12" t="s">
         <v>179</v>
       </c>
@@ -2570,18 +2573,14 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="B64">
-        <v>1200</v>
-      </c>
-      <c r="C64">
-        <v>1200</v>
+        <v>230</v>
       </c>
       <c r="D64" t="s">
-        <v>230</v>
-      </c>
-      <c r="E64" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
       <c r="F64" s="12" t="s">
         <v>179</v>
       </c>
@@ -2590,63 +2589,108 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="13" t="s">
         <v>231</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E65" t="s">
-        <v>54</v>
-      </c>
-      <c r="F65" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="G65" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G65" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="14" t="s">
-        <v>232</v>
+      <c r="A66">
+        <v>1935968</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="E66" t="s">
         <v>233</v>
       </c>
-      <c r="F66" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="G66" s="15" t="s">
-        <v>177</v>
+      <c r="F66" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="G66" s="12" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>1935968</v>
+      <c r="A67" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
+        <v>50</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G67" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F67" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="G67" s="15" t="s">
-        <v>180</v>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D69" t="s">
+        <v>45</v>
+      </c>
+      <c r="E69" t="s">
+        <v>51</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D70" t="s">
+        <v>44</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G61" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:G60" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F2:F686" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F685" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Caja de Ahorro,Tarjeta de crédito"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G686" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G685" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"Ingresos,Gastos"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2658,13 +2702,13 @@
           <x14:formula1>
             <xm:f>Categorías!$A$2:$A$27</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D686</xm:sqref>
+          <xm:sqref>D2:D685</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>Categorías!$D$2:$D$62</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E686</xm:sqref>
+          <xm:sqref>E2:E685</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
